--- a/XLibur.Tests/Resource/Examples/Styles/UsingColors.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/UsingColors.xlsx
@@ -505,93 +505,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:B18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="45.424911" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625"/>
+    <x:col min="2" max="2" width="45.424911" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="1"/>
-      <x:c r="B1" s="0" t="s">
+      <x:c r="B1" t="s">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="2"/>
-      <x:c r="B2" s="0" t="s">
+      <x:c r="B2" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="3"/>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="B4" t="s">
         <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="3"/>
-      <x:c r="B5" s="0" t="s">
+      <x:c r="B5" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="4"/>
-      <x:c r="B6" s="0" t="s">
+      <x:c r="B6" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="3"/>
-      <x:c r="B7" s="0" t="s">
+      <x:c r="B7" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1"/>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="B9" t="s">
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="5"/>
-      <x:c r="B11" s="0" t="s">
+      <x:c r="B11" t="s">
         <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="6"/>
-      <x:c r="B13" s="0" t="s">
+      <x:c r="B13" t="s">
         <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="7"/>
-      <x:c r="B15" s="0" t="s">
+      <x:c r="B15" t="s">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="8"/>
-      <x:c r="B17" s="0" t="s">
+      <x:c r="B17" t="s">
         <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="9"/>
-      <x:c r="B18" s="0" t="s">
+      <x:c r="B18" t="s">
         <x:v>11</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Styles/UsingColors.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/UsingColors.xlsx
@@ -509,7 +509,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="45.424911" customWidth="1"/>
+    <x:col min="2" max="2" width="44.282054" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">

--- a/XLibur.Tests/Resource/Examples/Styles/UsingColors.xlsx
+++ b/XLibur.Tests/Resource/Examples/Styles/UsingColors.xlsx
@@ -508,8 +508,8 @@
   <x:dimension ref="A1:B18"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625"/>
-    <x:col min="2" max="2" width="44.282054" customWidth="1"/>
+    <x:col min="1" max="1" width="9.144286"/>
+    <x:col min="2" max="2" width="44.285714" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
